--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556932625</v>
+        <v>46157.93118642188</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118642188</v>
+        <v>46157.93140332528</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93140332528</v>
+        <v>46157.93386926784</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93386926784</v>
+        <v>46157.93698866969</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93698866969</v>
+        <v>46158.28206422824</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206422824</v>
+        <v>46158.29655842975</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29655842975</v>
+        <v>46158.29795608902</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29795608902</v>
+        <v>46158.33373078441</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33373078441</v>
+        <v>46158.37226440533</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Сентябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37226440533</v>
+        <v>46158.37277042726</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
